--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/Chapter1.xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/Chapter1.xlsx
@@ -640,12 +640,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Player_Surprised</t>
+          <t>Player_Normal</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Player_Surprised</t>
+          <t>Player_Normal</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Player_Surprised</t>
+          <t>Player_Normal</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Player_Shock</t>
+          <t>Player_Angry</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Player_Shock</t>
+          <t>Player_Angry</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Player_Shock</t>
+          <t>Player_Angry</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Player_Kneel</t>
+          <t>Player_Embarrassed</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>本行必须用 charmove：左槽已显式填写 Player_Kneel，否则命令无效</t>
+          <t>本行必须用 charmove：左槽已显式填写 Player_Embarrassed，否则命令无效</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Player_Kneel</t>
+          <t>Player_Embarrassed</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Player_Kneel</t>
+          <t>Player_Embarrassed</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Player_Kneel</t>
+          <t>Player_Embarrassed</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Player_Surprised</t>
+          <t>Player_Normal</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Player_Surprised</t>
+          <t>Player_Normal</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Player_Surprised</t>
+          <t>Player_Normal</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Player_Surprised</t>
+          <t>Player_Normal</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/Chapter1.xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/Chapter1.xlsx
@@ -594,11 +594,7 @@
           <t>Hypnos</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Hypnos_Normal</t>
-        </is>
-      </c>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -638,11 +634,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Player_Normal</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -682,11 +674,7 @@
           <t>Hypnos</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Hypnos_Smile</t>
-        </is>
-      </c>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -758,11 +746,7 @@
           <t>Hypnos</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Hypnos_Normal</t>
-        </is>
-      </c>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -798,11 +782,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Player_Angry</t>
-        </is>
-      </c>
+      <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Player_Angry</t>
@@ -878,11 +858,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Player_Angry</t>
-        </is>
-      </c>
+      <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Player_Angry</t>
@@ -954,11 +930,7 @@
           <t>Hypnos</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Hypnos_Normal</t>
-        </is>
-      </c>
+      <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Player_Angry</t>
@@ -1030,11 +1002,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Player_Normal</t>
-        </is>
-      </c>
+      <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -1110,11 +1078,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Player_Embarrassed</t>
-        </is>
-      </c>
+      <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Player_Embarrassed</t>
@@ -1186,11 +1150,7 @@
           <t>Hypnos</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Hypnos_Normal</t>
-        </is>
-      </c>
+      <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -1270,11 +1230,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Player_Normal</t>
-        </is>
-      </c>
+      <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -1358,11 +1314,7 @@
           <t>Mimi</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Mimi_Proud</t>
-        </is>
-      </c>
+      <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
